--- a/Layout_Informacion_Basica.xlsx
+++ b/Layout_Informacion_Basica.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LAYOUT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INMUEBLE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="LAYOUT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Catálogos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="INMUEBLE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:BA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -563,36 +563,37 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="26" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="16" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
     <col width="14" customWidth="1" min="43" max="43"/>
     <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
-    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -618,12 +619,12 @@
           <t>DATOS DEL SERVIDOR PÚBLICO</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr">
+      <c r="AK2" s="4" t="inlineStr">
         <is>
           <t>PERSONA-PUESTO / FECHAS</t>
         </is>
       </c>
-      <c r="AS2" s="5" t="inlineStr">
+      <c r="AT2" s="5" t="inlineStr">
         <is>
           <t>RESPONSABILIDADES</t>
         </is>
@@ -743,176 +744,181 @@
           <t>CURP</t>
         </is>
       </c>
-      <c r="V3" s="6" t="inlineStr">
+      <c r="V3" s="7" t="inlineStr">
+        <is>
+          <t>DETERMINANTE</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>NOMBRE</t>
         </is>
       </c>
-      <c r="W3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>PRIMER
 APELLIDO</t>
         </is>
       </c>
-      <c r="X3" s="7" t="inlineStr">
+      <c r="Y3" s="7" t="inlineStr">
         <is>
           <t>SEGUNDO
 APELLIDO</t>
         </is>
       </c>
-      <c r="Y3" s="6" t="inlineStr">
+      <c r="Z3" s="6" t="inlineStr">
         <is>
           <t>FECHA
 NACIMIENTO</t>
         </is>
       </c>
-      <c r="Z3" s="6" t="inlineStr">
+      <c r="AA3" s="6" t="inlineStr">
         <is>
           <t>GENERO</t>
         </is>
       </c>
-      <c r="AA3" s="7" t="inlineStr">
+      <c r="AB3" s="7" t="inlineStr">
         <is>
           <t>ESTADO
 CIVIL</t>
         </is>
       </c>
-      <c r="AB3" s="7" t="inlineStr">
+      <c r="AC3" s="7" t="inlineStr">
         <is>
           <t>ENTIDAD</t>
         </is>
       </c>
-      <c r="AC3" s="7" t="inlineStr">
+      <c r="AD3" s="7" t="inlineStr">
         <is>
           <t>PAIS</t>
         </is>
       </c>
-      <c r="AD3" s="7" t="inlineStr">
+      <c r="AE3" s="7" t="inlineStr">
         <is>
           <t>CORREO
 ELECTRONICO</t>
         </is>
       </c>
-      <c r="AE3" s="6" t="inlineStr">
+      <c r="AF3" s="6" t="inlineStr">
         <is>
           <t>ISS</t>
         </is>
       </c>
-      <c r="AF3" s="7" t="inlineStr">
+      <c r="AG3" s="7" t="inlineStr">
         <is>
           <t>NSS</t>
         </is>
       </c>
-      <c r="AG3" s="7" t="inlineStr">
+      <c r="AH3" s="7" t="inlineStr">
         <is>
           <t>CENTRO
 TRABAJO</t>
         </is>
       </c>
-      <c r="AH3" s="6" t="inlineStr">
+      <c r="AI3" s="6" t="inlineStr">
         <is>
           <t>SINDICALIZADO</t>
         </is>
       </c>
-      <c r="AI3" s="7" t="inlineStr">
+      <c r="AJ3" s="7" t="inlineStr">
         <is>
           <t>SINDICATO</t>
         </is>
       </c>
-      <c r="AJ3" s="6" t="inlineStr">
+      <c r="AK3" s="6" t="inlineStr">
         <is>
           <t>ORDP
 Decl.Patrimonial</t>
         </is>
       </c>
-      <c r="AK3" s="7" t="inlineStr">
+      <c r="AL3" s="7" t="inlineStr">
         <is>
           <t>TIPO
 DECLARACION</t>
         </is>
       </c>
-      <c r="AL3" s="6" t="inlineStr">
+      <c r="AM3" s="6" t="inlineStr">
         <is>
           <t>OPAAER
 Entrega-Recep.</t>
         </is>
       </c>
-      <c r="AM3" s="6" t="inlineStr">
+      <c r="AN3" s="6" t="inlineStr">
         <is>
           <t>RENCTA
 Rinde Cuentas</t>
         </is>
       </c>
-      <c r="AN3" s="6" t="inlineStr">
+      <c r="AO3" s="6" t="inlineStr">
         <is>
           <t>PRDMIS
 Info Sensible</t>
         </is>
       </c>
-      <c r="AO3" s="6" t="inlineStr">
+      <c r="AP3" s="6" t="inlineStr">
         <is>
           <t>OTRA
 PLAZA</t>
         </is>
       </c>
-      <c r="AP3" s="7" t="inlineStr">
+      <c r="AQ3" s="7" t="inlineStr">
         <is>
           <t>FECHA INGRESO
 GOBIERNO</t>
         </is>
       </c>
-      <c r="AQ3" s="7" t="inlineStr">
+      <c r="AR3" s="7" t="inlineStr">
         <is>
           <t>FECHA INGRESO
 DEP.</t>
         </is>
       </c>
-      <c r="AR3" s="7" t="inlineStr">
+      <c r="AS3" s="7" t="inlineStr">
         <is>
           <t>FECHA INGRESO
 PUESTO</t>
         </is>
       </c>
-      <c r="AS3" s="7" t="inlineStr">
+      <c r="AT3" s="7" t="inlineStr">
         <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="AT3" s="6" t="inlineStr">
+      <c r="AU3" s="6" t="inlineStr">
         <is>
           <t>PARCONPUB
 Partic.Contr.</t>
         </is>
       </c>
-      <c r="AU3" s="7" t="inlineStr">
+      <c r="AV3" s="7" t="inlineStr">
         <is>
           <t>CONTRATACION
 PUBLICA</t>
         </is>
       </c>
-      <c r="AV3" s="6" t="inlineStr">
+      <c r="AW3" s="6" t="inlineStr">
         <is>
           <t>PARCON
 Partic.Conces.</t>
         </is>
       </c>
-      <c r="AW3" s="7" t="inlineStr">
+      <c r="AX3" s="7" t="inlineStr">
         <is>
           <t>CONCESIONES</t>
         </is>
       </c>
-      <c r="AX3" s="6" t="inlineStr">
+      <c r="AY3" s="6" t="inlineStr">
         <is>
           <t>PARENA
 Partic.Enaj.</t>
         </is>
       </c>
-      <c r="AY3" s="7" t="inlineStr">
+      <c r="AZ3" s="7" t="inlineStr">
         <is>
           <t>ENAJENACION</t>
         </is>
       </c>
-      <c r="AZ3" s="7" t="inlineStr">
+      <c r="BA3" s="7" t="inlineStr">
         <is>
           <t>INMUEBLE</t>
         </is>
@@ -1024,157 +1030,157 @@
           <t>SASE870301MTCNNR00</t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="W4" s="8" t="inlineStr">
         <is>
           <t>ERIKA</t>
         </is>
       </c>
-      <c r="W4" s="8" t="inlineStr">
+      <c r="X4" s="8" t="inlineStr">
         <is>
           <t>SANCHEZ</t>
         </is>
       </c>
-      <c r="X4" s="8" t="inlineStr">
+      <c r="Y4" s="8" t="inlineStr">
         <is>
           <t>SANCHEZ o NULL</t>
         </is>
       </c>
-      <c r="Y4" s="8" t="inlineStr">
+      <c r="Z4" s="8" t="inlineStr">
         <is>
           <t>01/10/1990</t>
         </is>
       </c>
-      <c r="Z4" s="8" t="inlineStr">
+      <c r="AA4" s="8" t="inlineStr">
         <is>
           <t>M o F</t>
         </is>
       </c>
-      <c r="AA4" s="8" t="inlineStr">
+      <c r="AB4" s="8" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="AB4" s="8" t="inlineStr">
+      <c r="AC4" s="8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AC4" s="8" t="inlineStr">
+      <c r="AD4" s="8" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AD4" s="8" t="inlineStr">
+      <c r="AE4" s="8" t="inlineStr">
         <is>
           <t>nombre@tabasco.gob.mx</t>
         </is>
       </c>
-      <c r="AE4" s="8" t="inlineStr">
+      <c r="AF4" s="8" t="inlineStr">
         <is>
           <t>ISSET</t>
         </is>
       </c>
-      <c r="AF4" s="8" t="inlineStr">
+      <c r="AG4" s="8" t="inlineStr">
         <is>
           <t>210887 o NULL</t>
         </is>
       </c>
-      <c r="AG4" s="8" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AH4" s="8" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AI4" s="8" t="inlineStr">
+        <is>
           <t>S o N</t>
         </is>
       </c>
-      <c r="AI4" s="8" t="inlineStr">
+      <c r="AJ4" s="8" t="inlineStr">
         <is>
           <t>SUTSET o NULL</t>
         </is>
       </c>
-      <c r="AJ4" s="8" t="inlineStr">
+      <c r="AK4" s="8" t="inlineStr">
         <is>
           <t>S/N/NULL</t>
         </is>
       </c>
-      <c r="AK4" s="8" t="inlineStr">
+      <c r="AL4" s="8" t="inlineStr">
         <is>
           <t>C/R/S/NULL</t>
         </is>
       </c>
-      <c r="AL4" s="8" t="inlineStr">
+      <c r="AM4" s="8" t="inlineStr">
         <is>
           <t>S/N/NULL</t>
         </is>
       </c>
-      <c r="AM4" s="8" t="inlineStr">
+      <c r="AN4" s="8" t="inlineStr">
         <is>
           <t>S/N/NULL</t>
         </is>
       </c>
-      <c r="AN4" s="8" t="inlineStr">
+      <c r="AO4" s="8" t="inlineStr">
         <is>
           <t>S/N/NULL</t>
         </is>
       </c>
-      <c r="AO4" s="8" t="inlineStr">
+      <c r="AP4" s="8" t="inlineStr">
         <is>
           <t>S o N</t>
         </is>
       </c>
-      <c r="AP4" s="8" t="inlineStr">
+      <c r="AQ4" s="8" t="inlineStr">
         <is>
           <t>01/10/2013</t>
         </is>
       </c>
-      <c r="AQ4" s="8" t="inlineStr">
+      <c r="AR4" s="8" t="inlineStr">
         <is>
           <t>01/10/2013</t>
         </is>
       </c>
-      <c r="AR4" s="8" t="inlineStr">
+      <c r="AS4" s="8" t="inlineStr">
         <is>
           <t>01/10/2013</t>
         </is>
       </c>
-      <c r="AS4" s="8" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AT4" s="8" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AU4" s="8" t="inlineStr">
+        <is>
           <t>S o N</t>
         </is>
       </c>
-      <c r="AU4" s="8" t="inlineStr">
+      <c r="AV4" s="8" t="inlineStr">
         <is>
           <t>A/B/C/NULL</t>
         </is>
       </c>
-      <c r="AV4" s="8" t="inlineStr">
+      <c r="AW4" s="8" t="inlineStr">
         <is>
           <t>S o N</t>
         </is>
       </c>
-      <c r="AW4" s="8" t="inlineStr">
+      <c r="AX4" s="8" t="inlineStr">
         <is>
           <t>A/B/C/NULL</t>
         </is>
       </c>
-      <c r="AX4" s="8" t="inlineStr">
+      <c r="AY4" s="8" t="inlineStr">
         <is>
           <t>S o N</t>
         </is>
       </c>
-      <c r="AY4" s="8" t="inlineStr">
+      <c r="AZ4" s="8" t="inlineStr">
         <is>
           <t>A/B/C/NULL</t>
         </is>
       </c>
-      <c r="AZ4" s="8" t="inlineStr">
+      <c r="BA4" s="8" t="inlineStr">
         <is>
           <t>IT001 o NULL</t>
         </is>
@@ -1270,155 +1276,155 @@
           <t>SASE870301MTCNNR00</t>
         </is>
       </c>
-      <c r="V5" s="9" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>ERIKA</t>
         </is>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="X5" s="9" t="inlineStr">
         <is>
           <t>SANCHEZ</t>
         </is>
       </c>
-      <c r="X5" s="9" t="inlineStr">
+      <c r="Y5" s="9" t="inlineStr">
         <is>
           <t>SANCHEZ</t>
         </is>
       </c>
-      <c r="Y5" s="9" t="inlineStr">
+      <c r="Z5" s="9" t="inlineStr">
         <is>
           <t>01/10/1987</t>
         </is>
       </c>
-      <c r="Z5" s="9" t="inlineStr">
+      <c r="AA5" s="9" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AA5" s="9" t="inlineStr">
+      <c r="AB5" s="9" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="AB5" s="9" t="inlineStr">
+      <c r="AC5" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AC5" s="9" t="inlineStr">
+      <c r="AD5" s="9" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AD5" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AE5" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AF5" s="9" t="inlineStr">
+        <is>
           <t>ISSET</t>
         </is>
       </c>
-      <c r="AF5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
         <v>210887</v>
       </c>
-      <c r="AG5" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AH5" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AI5" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AI5" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AJ5" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AK5" s="9" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AK5" s="9" t="inlineStr">
+      <c r="AL5" s="9" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AL5" s="9" t="inlineStr">
+      <c r="AM5" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AM5" s="9" t="inlineStr">
+      <c r="AN5" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AN5" s="9" t="inlineStr">
+      <c r="AO5" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AO5" s="9" t="inlineStr">
+      <c r="AP5" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AP5" s="9" t="inlineStr">
+      <c r="AQ5" s="9" t="inlineStr">
         <is>
           <t>01/10/2013</t>
         </is>
       </c>
-      <c r="AQ5" s="9" t="inlineStr">
+      <c r="AR5" s="9" t="inlineStr">
         <is>
           <t>01/10/2013</t>
         </is>
       </c>
-      <c r="AR5" s="9" t="inlineStr">
+      <c r="AS5" s="9" t="inlineStr">
         <is>
           <t>01/10/2013</t>
         </is>
       </c>
-      <c r="AS5" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AT5" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AU5" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AU5" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AV5" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AW5" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AW5" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AX5" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AY5" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AY5" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AZ5" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="BA5" s="9" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -1514,155 +1520,155 @@
           <t>GOCI750923HTCNRS04</t>
         </is>
       </c>
-      <c r="V6" s="10" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>ISIDRO</t>
         </is>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="X6" s="10" t="inlineStr">
         <is>
           <t>GONZALEZ</t>
         </is>
       </c>
-      <c r="X6" s="10" t="inlineStr">
+      <c r="Y6" s="10" t="inlineStr">
         <is>
           <t>DE LA CRUZ</t>
         </is>
       </c>
-      <c r="Y6" s="10" t="inlineStr">
+      <c r="Z6" s="10" t="inlineStr">
         <is>
           <t>23/09/1975</t>
         </is>
       </c>
-      <c r="Z6" s="10" t="inlineStr">
+      <c r="AA6" s="10" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AA6" s="10" t="inlineStr">
+      <c r="AB6" s="10" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="AB6" s="10" t="inlineStr">
+      <c r="AC6" s="10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AC6" s="10" t="inlineStr">
+      <c r="AD6" s="10" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AD6" s="10" t="inlineStr">
+      <c r="AE6" s="10" t="inlineStr">
         <is>
           <t>isidro.gonzalez@tabasco.gob.mx</t>
         </is>
       </c>
-      <c r="AE6" s="10" t="inlineStr">
+      <c r="AF6" s="10" t="inlineStr">
         <is>
           <t>ISSET</t>
         </is>
       </c>
-      <c r="AF6" s="10" t="n">
+      <c r="AG6" s="10" t="n">
         <v>1236789</v>
       </c>
-      <c r="AG6" s="10" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AH6" s="10" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AI6" s="10" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AI6" s="10" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AJ6" s="10" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AK6" s="10" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AK6" s="10" t="inlineStr">
+      <c r="AL6" s="10" t="inlineStr">
         <is>
           <t>COMPLETA</t>
         </is>
       </c>
-      <c r="AL6" s="10" t="inlineStr">
+      <c r="AM6" s="10" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AM6" s="10" t="inlineStr">
+      <c r="AN6" s="10" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AN6" s="10" t="inlineStr">
+      <c r="AO6" s="10" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AO6" s="10" t="inlineStr">
+      <c r="AP6" s="10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AP6" s="10" t="inlineStr">
+      <c r="AQ6" s="10" t="inlineStr">
         <is>
           <t>01/01/1998</t>
         </is>
       </c>
-      <c r="AQ6" s="10" t="inlineStr">
+      <c r="AR6" s="10" t="inlineStr">
         <is>
           <t>01/01/1998</t>
         </is>
       </c>
-      <c r="AR6" s="10" t="inlineStr">
+      <c r="AS6" s="10" t="inlineStr">
         <is>
           <t>01/10/2024</t>
         </is>
       </c>
-      <c r="AS6" s="10" t="inlineStr">
+      <c r="AT6" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AT6" s="10" t="inlineStr">
+      <c r="AU6" s="10" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AU6" s="10" t="inlineStr">
+      <c r="AV6" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AV6" s="10" t="inlineStr">
+      <c r="AW6" s="10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AW6" s="10" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AX6" s="10" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AY6" s="10" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AY6" s="10" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AZ6" s="10" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="BA6" s="10" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -1758,61 +1764,56 @@
           <t>RAML850315MTCMRS06</t>
         </is>
       </c>
-      <c r="V7" s="9" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>LAURA</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="X7" s="9" t="inlineStr">
         <is>
           <t>RAMIREZ</t>
         </is>
       </c>
-      <c r="X7" s="9" t="inlineStr">
+      <c r="Y7" s="9" t="inlineStr">
         <is>
           <t>MARTINEZ</t>
         </is>
       </c>
-      <c r="Y7" s="9" t="inlineStr">
+      <c r="Z7" s="9" t="inlineStr">
         <is>
           <t>15/03/1985</t>
         </is>
       </c>
-      <c r="Z7" s="9" t="inlineStr">
+      <c r="AA7" s="9" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AA7" s="9" t="inlineStr">
+      <c r="AB7" s="9" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="AB7" s="9" t="inlineStr">
+      <c r="AC7" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AC7" s="9" t="inlineStr">
+      <c r="AD7" s="9" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AD7" s="9" t="inlineStr">
+      <c r="AE7" s="9" t="inlineStr">
         <is>
           <t>laura.ramirez@tabasco.gob.mx</t>
         </is>
       </c>
-      <c r="AE7" s="9" t="inlineStr">
+      <c r="AF7" s="9" t="inlineStr">
         <is>
           <t>ISSET</t>
         </is>
       </c>
-      <c r="AF7" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AG7" s="9" t="inlineStr">
         <is>
           <t>NULL</t>
@@ -1820,95 +1821,100 @@
       </c>
       <c r="AH7" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AI7" s="9" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AI7" s="9" t="inlineStr">
+      <c r="AJ7" s="9" t="inlineStr">
         <is>
           <t>SUTSET</t>
         </is>
       </c>
-      <c r="AJ7" s="9" t="inlineStr">
+      <c r="AK7" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AK7" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AL7" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AM7" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AM7" s="9" t="inlineStr">
+      <c r="AN7" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AN7" s="9" t="inlineStr">
+      <c r="AO7" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AO7" s="9" t="inlineStr">
+      <c r="AP7" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AP7" s="9" t="inlineStr">
+      <c r="AQ7" s="9" t="inlineStr">
         <is>
           <t>15/08/2010</t>
         </is>
       </c>
-      <c r="AQ7" s="9" t="inlineStr">
+      <c r="AR7" s="9" t="inlineStr">
         <is>
           <t>15/08/2010</t>
         </is>
       </c>
-      <c r="AR7" s="9" t="inlineStr">
+      <c r="AS7" s="9" t="inlineStr">
         <is>
           <t>01/09/2022</t>
         </is>
       </c>
-      <c r="AS7" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AT7" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AU7" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AU7" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AV7" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AW7" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AW7" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AX7" s="9" t="inlineStr">
         <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="AY7" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AY7" s="9" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="AZ7" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="BA7" s="9" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -1916,12 +1922,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:AZ1"/>
+    <mergeCell ref="S2:AJ2"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="AJ2:AR2"/>
-    <mergeCell ref="AS2:AZ2"/>
-    <mergeCell ref="S2:AI2"/>
+    <mergeCell ref="AK2:AS2"/>
+    <mergeCell ref="AT2:BA2"/>
     <mergeCell ref="F2:R2"/>
+    <mergeCell ref="A1:BA1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
